--- a/outputs/15671.xlsx
+++ b/outputs/15671.xlsx
@@ -369,7 +369,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="str">
-        <f aca="false">TEXT(A1, "0")</f>
+        <f aca="false">TEXT(A1,"0")</f>
         <v>911313316543722</v>
       </c>
     </row>
@@ -378,7 +378,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f aca="false">TEXT(A2, "0")</f>
+        <f aca="false">TEXT(A2,"0")</f>
         <v>913313331154233</v>
       </c>
     </row>
@@ -387,7 +387,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">TEXT(A3, "0")</f>
+        <f aca="false">TEXT(A3,"0")</f>
         <v>913313331477316</v>
       </c>
     </row>
@@ -396,7 +396,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f aca="false">TEXT(A4, "0")</f>
+        <f aca="false">TEXT(A4,"0")</f>
         <v>913313323763536</v>
       </c>
     </row>
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f aca="false">TEXT(A5, "0")</f>
+        <f aca="false">TEXT(A5,"0")</f>
         <v>913313323763473</v>
       </c>
     </row>
@@ -414,7 +414,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f aca="false">TEXT(A6, "0")</f>
+        <f aca="false">TEXT(A6,"0")</f>
         <v>913313329226819</v>
       </c>
     </row>
@@ -423,7 +423,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f aca="false">TEXT(A7, "0")</f>
+        <f aca="false">TEXT(A7,"0")</f>
         <v>913313343567715</v>
       </c>
     </row>
@@ -432,7 +432,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f aca="false">TEXT(A8, "0")</f>
+        <f aca="false">TEXT(A8,"0")</f>
         <v>913313329228226</v>
       </c>
     </row>
@@ -441,7 +441,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f aca="false">TEXT(A9, "0")</f>
+        <f aca="false">TEXT(A9,"0")</f>
         <v>911313318355914</v>
       </c>
     </row>
@@ -450,7 +450,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f aca="false">TEXT(A10, "0")</f>
+        <f aca="false">TEXT(A10,"0")</f>
         <v>913313327498337</v>
       </c>
     </row>
@@ -459,7 +459,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f aca="false">TEXT(A11, "0")</f>
+        <f aca="false">TEXT(A11,"0")</f>
         <v>913313327497567</v>
       </c>
     </row>
@@ -468,7 +468,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f aca="false">TEXT(A12, "0")</f>
+        <f aca="false">TEXT(A12,"0")</f>
         <v>913313327497499</v>
       </c>
     </row>
@@ -477,7 +477,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f aca="false">TEXT(A13, "0")</f>
+        <f aca="false">TEXT(A13,"0")</f>
         <v>911313335259935</v>
       </c>
     </row>
@@ -486,7 +486,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f aca="false">TEXT(A14, "0")</f>
+        <f aca="false">TEXT(A14,"0")</f>
         <v>911313335263142</v>
       </c>
     </row>
@@ -495,7 +495,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f aca="false">TEXT(A15, "0")</f>
+        <f aca="false">TEXT(A15,"0")</f>
         <v>911313335259896</v>
       </c>
     </row>
@@ -504,7 +504,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f aca="false">TEXT(A16, "0")</f>
+        <f aca="false">TEXT(A16,"0")</f>
         <v>911313317514666</v>
       </c>
     </row>
@@ -513,7 +513,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f aca="false">TEXT(A17, "0")</f>
+        <f aca="false">TEXT(A17,"0")</f>
         <v>911313335263334</v>
       </c>
     </row>
@@ -522,7 +522,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f aca="false">TEXT(A18, "0")</f>
+        <f aca="false">TEXT(A18,"0")</f>
         <v>911313335263168</v>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f aca="false">TEXT(A19, "0")</f>
+        <f aca="false">TEXT(A19,"0")</f>
         <v>911313335263133</v>
       </c>
     </row>
@@ -540,7 +540,7 @@
         <v>911313335263126</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f aca="false">TEXT(A20, "0")</f>
+        <f aca="false">TEXT(A20,"0")</f>
         <v>911313335263126</v>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>911313339912113</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f aca="false">TEXT(A21, "0")</f>
+        <f aca="false">TEXT(A21,"0")</f>
         <v>911313339912113</v>
       </c>
     </row>
@@ -558,7 +558,7 @@
         <v>911313339919243</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f aca="false">TEXT(A22, "0")</f>
+        <f aca="false">TEXT(A22,"0")</f>
         <v>911313339919243</v>
       </c>
     </row>
@@ -567,7 +567,7 @@
         <v>911313335263317</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f aca="false">TEXT(A23, "0")</f>
+        <f aca="false">TEXT(A23,"0")</f>
         <v>911313335263317</v>
       </c>
     </row>
@@ -576,7 +576,7 @@
         <v>911313339919237</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f aca="false">TEXT(A24, "0")</f>
+        <f aca="false">TEXT(A24,"0")</f>
         <v>911313339919237</v>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>911313339919154</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f aca="false">TEXT(A25, "0")</f>
+        <f aca="false">TEXT(A25,"0")</f>
         <v>911313339919154</v>
       </c>
     </row>
@@ -594,7 +594,7 @@
         <v>911313339912184</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f aca="false">TEXT(A26, "0")</f>
+        <f aca="false">TEXT(A26,"0")</f>
         <v>911313339912184</v>
       </c>
     </row>
@@ -603,7 +603,7 @@
         <v>911313339919374</v>
       </c>
       <c r="B27" s="1" t="str">
-        <f aca="false">TEXT(A27, "0")</f>
+        <f aca="false">TEXT(A27,"0")</f>
         <v>911313339919374</v>
       </c>
     </row>
@@ -612,7 +612,7 @@
         <v>911313325535274</v>
       </c>
       <c r="B28" s="1" t="str">
-        <f aca="false">TEXT(A28, "0")</f>
+        <f aca="false">TEXT(A28,"0")</f>
         <v>911313325535274</v>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>911313339919133</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f aca="false">TEXT(A29, "0")</f>
+        <f aca="false">TEXT(A29,"0")</f>
         <v>911313339919133</v>
       </c>
     </row>
@@ -630,7 +630,7 @@
         <v>911313339919554</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f aca="false">TEXT(A30, "0")</f>
+        <f aca="false">TEXT(A30,"0")</f>
         <v>911313339919554</v>
       </c>
     </row>
@@ -639,7 +639,7 @@
         <v>911313323273154</v>
       </c>
       <c r="B31" s="1" t="str">
-        <f aca="false">TEXT(A31, "0")</f>
+        <f aca="false">TEXT(A31,"0")</f>
         <v>911313323273154</v>
       </c>
     </row>
@@ -648,7 +648,7 @@
         <v>911313323271584</v>
       </c>
       <c r="B32" s="1" t="str">
-        <f aca="false">TEXT(A32, "0")</f>
+        <f aca="false">TEXT(A32,"0")</f>
         <v>911313323271584</v>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>911313321972636</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f aca="false">TEXT(A33, "0")</f>
+        <f aca="false">TEXT(A33,"0")</f>
         <v>911313321972636</v>
       </c>
     </row>
@@ -666,7 +666,7 @@
         <v>911313339919491</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f aca="false">TEXT(A34, "0")</f>
+        <f aca="false">TEXT(A34,"0")</f>
         <v>911313339919491</v>
       </c>
     </row>
@@ -675,7 +675,7 @@
         <v>911313339919541</v>
       </c>
       <c r="B35" s="1" t="str">
-        <f aca="false">TEXT(A35, "0")</f>
+        <f aca="false">TEXT(A35,"0")</f>
         <v>911313339919541</v>
       </c>
     </row>
@@ -684,7 +684,7 @@
         <v>911313333713585</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f aca="false">TEXT(A36, "0")</f>
+        <f aca="false">TEXT(A36,"0")</f>
         <v>911313333713585</v>
       </c>
     </row>
@@ -693,7 +693,7 @@
         <v>911313339919525</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f aca="false">TEXT(A37, "0")</f>
+        <f aca="false">TEXT(A37,"0")</f>
         <v>911313339919525</v>
       </c>
     </row>
@@ -702,7 +702,7 @@
         <v>911313311379177</v>
       </c>
       <c r="B38" s="1" t="str">
-        <f aca="false">TEXT(A38, "0")</f>
+        <f aca="false">TEXT(A38,"0")</f>
         <v>911313311379177</v>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>911313311378879</v>
       </c>
       <c r="B39" s="1" t="str">
-        <f aca="false">TEXT(A39, "0")</f>
+        <f aca="false">TEXT(A39,"0")</f>
         <v>911313311378879</v>
       </c>
     </row>
@@ -720,7 +720,7 @@
         <v>911313326167871</v>
       </c>
       <c r="B40" s="1" t="str">
-        <f aca="false">TEXT(A40, "0")</f>
+        <f aca="false">TEXT(A40,"0")</f>
         <v>911313326167871</v>
       </c>
     </row>
@@ -729,7 +729,7 @@
         <v>911313328482967</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f aca="false">TEXT(A41, "0")</f>
+        <f aca="false">TEXT(A41,"0")</f>
         <v>911313328482967</v>
       </c>
     </row>
@@ -738,7 +738,7 @@
         <v>911313311379212</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f aca="false">TEXT(A42, "0")</f>
+        <f aca="false">TEXT(A42,"0")</f>
         <v>911313311379212</v>
       </c>
     </row>
@@ -747,7 +747,7 @@
         <v>911313311379347</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f aca="false">TEXT(A43, "0")</f>
+        <f aca="false">TEXT(A43,"0")</f>
         <v>911313311379347</v>
       </c>
     </row>
@@ -756,7 +756,7 @@
         <v>911313311378714</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f aca="false">TEXT(A44, "0")</f>
+        <f aca="false">TEXT(A44,"0")</f>
         <v>911313311378714</v>
       </c>
     </row>
@@ -765,7 +765,7 @@
         <v>911313311378772</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f aca="false">TEXT(A45, "0")</f>
+        <f aca="false">TEXT(A45,"0")</f>
         <v>911313311378772</v>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>911313311379273</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f aca="false">TEXT(A46, "0")</f>
+        <f aca="false">TEXT(A46,"0")</f>
         <v>911313311379273</v>
       </c>
     </row>
@@ -783,7 +783,7 @@
         <v>911313326168231</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f aca="false">TEXT(A47, "0")</f>
+        <f aca="false">TEXT(A47,"0")</f>
         <v>911313326168231</v>
       </c>
     </row>
@@ -792,7 +792,7 @@
         <v>911313326167539</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f aca="false">TEXT(A48, "0")</f>
+        <f aca="false">TEXT(A48,"0")</f>
         <v>911313326167539</v>
       </c>
     </row>
@@ -801,7 +801,7 @@
         <v>911313337585156</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f aca="false">TEXT(A49, "0")</f>
+        <f aca="false">TEXT(A49,"0")</f>
         <v>911313337585156</v>
       </c>
     </row>
@@ -810,7 +810,7 @@
         <v>911313326167716</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f aca="false">TEXT(A50, "0")</f>
+        <f aca="false">TEXT(A50,"0")</f>
         <v>911313326167716</v>
       </c>
     </row>
@@ -819,7 +819,7 @@
         <v>911313341363835</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f aca="false">TEXT(A51, "0")</f>
+        <f aca="false">TEXT(A51,"0")</f>
         <v>911313341363835</v>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>911313342528582</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f aca="false">TEXT(A52, "0")</f>
+        <f aca="false">TEXT(A52,"0")</f>
         <v>911313342528582</v>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v>911313335848738</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f aca="false">TEXT(A53, "0")</f>
+        <f aca="false">TEXT(A53,"0")</f>
         <v>911313335848738</v>
       </c>
     </row>
@@ -846,7 +846,7 @@
         <v>911313342356121</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f aca="false">TEXT(A54, "0")</f>
+        <f aca="false">TEXT(A54,"0")</f>
         <v>911313342356121</v>
       </c>
     </row>
@@ -855,7 +855,7 @@
         <v>911313342436774</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f aca="false">TEXT(A55, "0")</f>
+        <f aca="false">TEXT(A55,"0")</f>
         <v>911313342436774</v>
       </c>
     </row>
@@ -864,7 +864,7 @@
         <v>913313323764367</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f aca="false">TEXT(A56, "0")</f>
+        <f aca="false">TEXT(A56,"0")</f>
         <v>913313323764367</v>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v>911313341359392</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f aca="false">TEXT(A57, "0")</f>
+        <f aca="false">TEXT(A57,"0")</f>
         <v>911313341359392</v>
       </c>
     </row>
@@ -882,7 +882,7 @@
         <v>911313341397769</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f aca="false">TEXT(A58, "0")</f>
+        <f aca="false">TEXT(A58,"0")</f>
         <v>911313341397769</v>
       </c>
     </row>
@@ -891,7 +891,7 @@
         <v>911313341398374</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f aca="false">TEXT(A59, "0")</f>
+        <f aca="false">TEXT(A59,"0")</f>
         <v>911313341398374</v>
       </c>
     </row>
@@ -900,7 +900,7 @@
         <v>911313341384271</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f aca="false">TEXT(A60, "0")</f>
+        <f aca="false">TEXT(A60,"0")</f>
         <v>911313341384271</v>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v>911313335848851</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f aca="false">TEXT(A61, "0")</f>
+        <f aca="false">TEXT(A61,"0")</f>
         <v>911313335848851</v>
       </c>
     </row>
@@ -918,7 +918,7 @@
         <v>911313335848691</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f aca="false">TEXT(A62, "0")</f>
+        <f aca="false">TEXT(A62,"0")</f>
         <v>911313335848691</v>
       </c>
     </row>
@@ -927,7 +927,7 @@
         <v>911313342373935</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f aca="false">TEXT(A63, "0")</f>
+        <f aca="false">TEXT(A63,"0")</f>
         <v>911313342373935</v>
       </c>
     </row>
@@ -936,7 +936,7 @@
         <v>911313342378244</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f aca="false">TEXT(A64, "0")</f>
+        <f aca="false">TEXT(A64,"0")</f>
         <v>911313342378244</v>
       </c>
     </row>
@@ -945,7 +945,7 @@
         <v>911313339963385</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f aca="false">TEXT(A65, "0")</f>
+        <f aca="false">TEXT(A65,"0")</f>
         <v>911313339963385</v>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>911313353823492</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f aca="false">TEXT(A66, "0")</f>
+        <f aca="false">TEXT(A66,"0")</f>
         <v>911313353823492</v>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>911313339963275</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f aca="false">TEXT(A67, "0")</f>
+        <f aca="false">TEXT(A67,"0")</f>
         <v>911313339963275</v>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>911313346969822</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f aca="false">TEXT(A68, "0")</f>
+        <f aca="false">TEXT(A68,"0")</f>
         <v>911313346969822</v>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>911313346969877</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f aca="false">TEXT(A69, "0")</f>
+        <f aca="false">TEXT(A69,"0")</f>
         <v>911313346969877</v>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>911313346969897</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f aca="false">TEXT(A70, "0")</f>
+        <f aca="false">TEXT(A70,"0")</f>
         <v>911313346969897</v>
       </c>
     </row>
@@ -999,7 +999,7 @@
         <v>911313339963974</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f aca="false">TEXT(A71, "0")</f>
+        <f aca="false">TEXT(A71,"0")</f>
         <v>911313339963974</v>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         <v>911313346969741</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f aca="false">TEXT(A72, "0")</f>
+        <f aca="false">TEXT(A72,"0")</f>
         <v>911313346969741</v>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         <v>911313346968933</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f aca="false">TEXT(A73, "0")</f>
+        <f aca="false">TEXT(A73,"0")</f>
         <v>911313346968933</v>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         <v>911313346968845</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f aca="false">TEXT(A74, "0")</f>
+        <f aca="false">TEXT(A74,"0")</f>
         <v>911313346968845</v>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>911313346968893</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f aca="false">TEXT(A75, "0")</f>
+        <f aca="false">TEXT(A75,"0")</f>
         <v>911313346968893</v>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
         <v>911313346969521</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f aca="false">TEXT(A76, "0")</f>
+        <f aca="false">TEXT(A76,"0")</f>
         <v>911313346969521</v>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         <v>912313332277984</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f aca="false">TEXT(A77, "0")</f>
+        <f aca="false">TEXT(A77,"0")</f>
         <v>912313332277984</v>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
         <v>911313346973974</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f aca="false">TEXT(A78, "0")</f>
+        <f aca="false">TEXT(A78,"0")</f>
         <v>911313346973974</v>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         <v>912313336735254</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f aca="false">TEXT(A79, "0")</f>
+        <f aca="false">TEXT(A79,"0")</f>
         <v>912313336735254</v>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         <v>912313312323463</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f aca="false">TEXT(A80, "0")</f>
+        <f aca="false">TEXT(A80,"0")</f>
         <v>912313312323463</v>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
         <v>912313312324933</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f aca="false">TEXT(A81, "0")</f>
+        <f aca="false">TEXT(A81,"0")</f>
         <v>912313312324933</v>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
         <v>912313315485231</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f aca="false">TEXT(A82, "0")</f>
+        <f aca="false">TEXT(A82,"0")</f>
         <v>912313315485231</v>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
         <v>912313322481343</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f aca="false">TEXT(A83, "0")</f>
+        <f aca="false">TEXT(A83,"0")</f>
         <v>912313322481343</v>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         <v>912313322967984</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f aca="false">TEXT(A84, "0")</f>
+        <f aca="false">TEXT(A84,"0")</f>
         <v>912313322967984</v>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         <v>912313321996395</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f aca="false">TEXT(A85, "0")</f>
+        <f aca="false">TEXT(A85,"0")</f>
         <v>912313321996395</v>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>912313322412523</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f aca="false">TEXT(A86, "0")</f>
+        <f aca="false">TEXT(A86,"0")</f>
         <v>912313322412523</v>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
         <v>912313321883546</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f aca="false">TEXT(A87, "0")</f>
+        <f aca="false">TEXT(A87,"0")</f>
         <v>912313321883546</v>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
         <v>912313322996335</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f aca="false">TEXT(A88, "0")</f>
+        <f aca="false">TEXT(A88,"0")</f>
         <v>912313322996335</v>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         <v>912313324374992</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f aca="false">TEXT(A89, "0")</f>
+        <f aca="false">TEXT(A89,"0")</f>
         <v>912313324374992</v>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         <v>912313321883523</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f aca="false">TEXT(A90, "0")</f>
+        <f aca="false">TEXT(A90,"0")</f>
         <v>912313321883523</v>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
         <v>912313323248455</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f aca="false">TEXT(A91, "0")</f>
+        <f aca="false">TEXT(A91,"0")</f>
         <v>912313323248455</v>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         <v>912313323159517</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f aca="false">TEXT(A92, "0")</f>
+        <f aca="false">TEXT(A92,"0")</f>
         <v>912313323159517</v>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
         <v>911313359632333</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f aca="false">TEXT(A93, "0")</f>
+        <f aca="false">TEXT(A93,"0")</f>
         <v>911313359632333</v>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
         <v>912313323251781</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f aca="false">TEXT(A94, "0")</f>
+        <f aca="false">TEXT(A94,"0")</f>
         <v>912313323251781</v>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         <v>912313323251723</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f aca="false">TEXT(A95, "0")</f>
+        <f aca="false">TEXT(A95,"0")</f>
         <v>912313323251723</v>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         <v>911313359632126</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f aca="false">TEXT(A96, "0")</f>
+        <f aca="false">TEXT(A96,"0")</f>
         <v>911313359632126</v>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
         <v>911313359632197</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f aca="false">TEXT(A97, "0")</f>
+        <f aca="false">TEXT(A97,"0")</f>
         <v>911313359632197</v>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>912313328496659</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f aca="false">TEXT(A98, "0")</f>
+        <f aca="false">TEXT(A98,"0")</f>
         <v>912313328496659</v>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         <v>912313333856698</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f aca="false">TEXT(A99, "0")</f>
+        <f aca="false">TEXT(A99,"0")</f>
         <v>912313333856698</v>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         <v>912313333553735</v>
       </c>
       <c r="B100" s="1" t="str">
-        <f aca="false">TEXT(A100, "0")</f>
+        <f aca="false">TEXT(A100,"0")</f>
         <v>912313333553735</v>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
         <v>912313334498964</v>
       </c>
       <c r="B101" s="1" t="str">
-        <f aca="false">TEXT(A101, "0")</f>
+        <f aca="false">TEXT(A101,"0")</f>
         <v>912313334498964</v>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
         <v>912313332836479</v>
       </c>
       <c r="B102" s="1" t="str">
-        <f aca="false">TEXT(A102, "0")</f>
+        <f aca="false">TEXT(A102,"0")</f>
         <v>912313332836479</v>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
         <v>912313324993178</v>
       </c>
       <c r="B103" s="1" t="str">
-        <f aca="false">TEXT(A103, "0")</f>
+        <f aca="false">TEXT(A103,"0")</f>
         <v>912313324993178</v>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>913313331146889</v>
       </c>
       <c r="B104" s="1" t="str">
-        <f aca="false">TEXT(A104, "0")</f>
+        <f aca="false">TEXT(A104,"0")</f>
         <v>913313331146889</v>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>912313336336423</v>
       </c>
       <c r="B105" s="1" t="str">
-        <f aca="false">TEXT(A105, "0")</f>
+        <f aca="false">TEXT(A105,"0")</f>
         <v>912313336336423</v>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         <v>912313332836486</v>
       </c>
       <c r="B106" s="1" t="str">
-        <f aca="false">TEXT(A106, "0")</f>
+        <f aca="false">TEXT(A106,"0")</f>
         <v>912313332836486</v>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
         <v>912313332838326</v>
       </c>
       <c r="B107" s="1" t="str">
-        <f aca="false">TEXT(A107, "0")</f>
+        <f aca="false">TEXT(A107,"0")</f>
         <v>912313332838326</v>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
         <v>912313341778877</v>
       </c>
       <c r="B108" s="1" t="str">
-        <f aca="false">TEXT(A108, "0")</f>
+        <f aca="false">TEXT(A108,"0")</f>
         <v>912313341778877</v>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
         <v>912313332834831</v>
       </c>
       <c r="B109" s="1" t="str">
-        <f aca="false">TEXT(A109, "0")</f>
+        <f aca="false">TEXT(A109,"0")</f>
         <v>912313332834831</v>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         <v>912313332832268</v>
       </c>
       <c r="B110" s="1" t="str">
-        <f aca="false">TEXT(A110, "0")</f>
+        <f aca="false">TEXT(A110,"0")</f>
         <v>912313332832268</v>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         <v>912313332839281</v>
       </c>
       <c r="B111" s="1" t="str">
-        <f aca="false">TEXT(A111, "0")</f>
+        <f aca="false">TEXT(A111,"0")</f>
         <v>912313332839281</v>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>912313332839253</v>
       </c>
       <c r="B112" s="1" t="str">
-        <f aca="false">TEXT(A112, "0")</f>
+        <f aca="false">TEXT(A112,"0")</f>
         <v>912313332839253</v>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>912313332839236</v>
       </c>
       <c r="B113" s="1" t="str">
-        <f aca="false">TEXT(A113, "0")</f>
+        <f aca="false">TEXT(A113,"0")</f>
         <v>912313332839236</v>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v>912313332839243</v>
       </c>
       <c r="B114" s="1" t="str">
-        <f aca="false">TEXT(A114, "0")</f>
+        <f aca="false">TEXT(A114,"0")</f>
         <v>912313332839243</v>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         <v>912313332832457</v>
       </c>
       <c r="B115" s="1" t="str">
-        <f aca="false">TEXT(A115, "0")</f>
+        <f aca="false">TEXT(A115,"0")</f>
         <v>912313332832457</v>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>912313332834514</v>
       </c>
       <c r="B116" s="1" t="str">
-        <f aca="false">TEXT(A116, "0")</f>
+        <f aca="false">TEXT(A116,"0")</f>
         <v>912313332834514</v>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v>912313332834468</v>
       </c>
       <c r="B117" s="1" t="str">
-        <f aca="false">TEXT(A117, "0")</f>
+        <f aca="false">TEXT(A117,"0")</f>
         <v>912313332834468</v>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
         <v>912313332833935</v>
       </c>
       <c r="B118" s="1" t="str">
-        <f aca="false">TEXT(A118, "0")</f>
+        <f aca="false">TEXT(A118,"0")</f>
         <v>912313332833935</v>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         <v>912313332834396</v>
       </c>
       <c r="B119" s="1" t="str">
-        <f aca="false">TEXT(A119, "0")</f>
+        <f aca="false">TEXT(A119,"0")</f>
         <v>912313332834396</v>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         <v>912313332834578</v>
       </c>
       <c r="B120" s="1" t="str">
-        <f aca="false">TEXT(A120, "0")</f>
+        <f aca="false">TEXT(A120,"0")</f>
         <v>912313332834578</v>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
         <v>912313332834423</v>
       </c>
       <c r="B121" s="1" t="str">
-        <f aca="false">TEXT(A121, "0")</f>
+        <f aca="false">TEXT(A121,"0")</f>
         <v>912313332834423</v>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
         <v>912313324994237</v>
       </c>
       <c r="B122" s="1" t="str">
-        <f aca="false">TEXT(A122, "0")</f>
+        <f aca="false">TEXT(A122,"0")</f>
         <v>912313324994237</v>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
         <v>912313332832534</v>
       </c>
       <c r="B123" s="1" t="str">
-        <f aca="false">TEXT(A123, "0")</f>
+        <f aca="false">TEXT(A123,"0")</f>
         <v>912313332832534</v>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         <v>912313332832567</v>
       </c>
       <c r="B124" s="1" t="str">
-        <f aca="false">TEXT(A124, "0")</f>
+        <f aca="false">TEXT(A124,"0")</f>
         <v>912313332832567</v>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         <v>912313332832547</v>
       </c>
       <c r="B125" s="1" t="str">
-        <f aca="false">TEXT(A125, "0")</f>
+        <f aca="false">TEXT(A125,"0")</f>
         <v>912313332832547</v>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
         <v>912313332834499</v>
       </c>
       <c r="B126" s="1" t="str">
-        <f aca="false">TEXT(A126, "0")</f>
+        <f aca="false">TEXT(A126,"0")</f>
         <v>912313332834499</v>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>912313332834695</v>
       </c>
       <c r="B127" s="1" t="str">
-        <f aca="false">TEXT(A127, "0")</f>
+        <f aca="false">TEXT(A127,"0")</f>
         <v>912313332834695</v>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
         <v>912313332834734</v>
       </c>
       <c r="B128" s="1" t="str">
-        <f aca="false">TEXT(A128, "0")</f>
+        <f aca="false">TEXT(A128,"0")</f>
         <v>912313332834734</v>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
         <v>912313332834671</v>
       </c>
       <c r="B129" s="1" t="str">
-        <f aca="false">TEXT(A129, "0")</f>
+        <f aca="false">TEXT(A129,"0")</f>
         <v>912313332834671</v>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         <v>913313321971378</v>
       </c>
       <c r="B130" s="1" t="str">
-        <f aca="false">TEXT(A130, "0")</f>
+        <f aca="false">TEXT(A130,"0")</f>
         <v>913313321971378</v>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>912313332832393</v>
       </c>
       <c r="B131" s="1" t="str">
-        <f aca="false">TEXT(A131, "0")</f>
+        <f aca="false">TEXT(A131,"0")</f>
         <v>912313332832393</v>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>912313332835737</v>
       </c>
       <c r="B132" s="1" t="str">
-        <f aca="false">TEXT(A132, "0")</f>
+        <f aca="false">TEXT(A132,"0")</f>
         <v>912313332835737</v>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>912313332832386</v>
       </c>
       <c r="B133" s="1" t="str">
-        <f aca="false">TEXT(A133, "0")</f>
+        <f aca="false">TEXT(A133,"0")</f>
         <v>912313332832386</v>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>912313357387367</v>
       </c>
       <c r="B134" s="1" t="str">
-        <f aca="false">TEXT(A134, "0")</f>
+        <f aca="false">TEXT(A134,"0")</f>
         <v>912313357387367</v>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         <v>912313357387383</v>
       </c>
       <c r="B135" s="1" t="str">
-        <f aca="false">TEXT(A135, "0")</f>
+        <f aca="false">TEXT(A135,"0")</f>
         <v>912313357387383</v>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
         <v>913313331146889</v>
       </c>
       <c r="B136" s="1" t="str">
-        <f aca="false">TEXT(A136, "0")</f>
+        <f aca="false">TEXT(A136,"0")</f>
         <v>913313331146889</v>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
         <v>913313328354248</v>
       </c>
       <c r="B137" s="1" t="str">
-        <f aca="false">TEXT(A137, "0")</f>
+        <f aca="false">TEXT(A137,"0")</f>
         <v>913313328354248</v>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
         <v>911313339919353</v>
       </c>
       <c r="B138" s="1" t="str">
-        <f aca="false">TEXT(A138, "0")</f>
+        <f aca="false">TEXT(A138,"0")</f>
         <v>911313339919353</v>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>913313327498311</v>
       </c>
       <c r="B139" s="1" t="str">
-        <f aca="false">TEXT(A139, "0")</f>
+        <f aca="false">TEXT(A139,"0")</f>
         <v>913313327498311</v>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         <v>913313327498573</v>
       </c>
       <c r="B140" s="1" t="str">
-        <f aca="false">TEXT(A140, "0")</f>
+        <f aca="false">TEXT(A140,"0")</f>
         <v>913313327498573</v>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
         <v>911313339963152</v>
       </c>
       <c r="B141" s="1" t="str">
-        <f aca="false">TEXT(A141, "0")</f>
+        <f aca="false">TEXT(A141,"0")</f>
         <v>911313339963152</v>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
         <v>911313339963234</v>
       </c>
       <c r="B142" s="1" t="str">
-        <f aca="false">TEXT(A142, "0")</f>
+        <f aca="false">TEXT(A142,"0")</f>
         <v>911313339963234</v>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
         <v>911313346969535</v>
       </c>
       <c r="B143" s="1" t="str">
-        <f aca="false">TEXT(A143, "0")</f>
+        <f aca="false">TEXT(A143,"0")</f>
         <v>911313346969535</v>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
         <v>911313346969961</v>
       </c>
       <c r="B144" s="1" t="str">
-        <f aca="false">TEXT(A144, "0")</f>
+        <f aca="false">TEXT(A144,"0")</f>
         <v>911313346969961</v>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         <v>912313337288138</v>
       </c>
       <c r="B145" s="1" t="str">
-        <f aca="false">TEXT(A145, "0")</f>
+        <f aca="false">TEXT(A145,"0")</f>
         <v>912313337288138</v>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
         <v>912313332838332</v>
       </c>
       <c r="B146" s="1" t="str">
-        <f aca="false">TEXT(A146, "0")</f>
+        <f aca="false">TEXT(A146,"0")</f>
         <v>912313332838332</v>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
         <v>913313338367633</v>
       </c>
       <c r="B147" s="1" t="str">
-        <f aca="false">TEXT(A147, "0")</f>
+        <f aca="false">TEXT(A147,"0")</f>
         <v>913313338367633</v>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
         <v>913313327497583</v>
       </c>
       <c r="B148" s="1" t="str">
-        <f aca="false">TEXT(A148, "0")</f>
+        <f aca="false">TEXT(A148,"0")</f>
         <v>913313327497583</v>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
         <v>911313335259919</v>
       </c>
       <c r="B149" s="1" t="str">
-        <f aca="false">TEXT(A149, "0")</f>
+        <f aca="false">TEXT(A149,"0")</f>
         <v>911313335259919</v>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
         <v>911313311377449</v>
       </c>
       <c r="B150" s="1" t="str">
-        <f aca="false">TEXT(A150, "0")</f>
+        <f aca="false">TEXT(A150,"0")</f>
         <v>911313311377449</v>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
         <v>911313326167733</v>
       </c>
       <c r="B151" s="1" t="str">
-        <f aca="false">TEXT(A151, "0")</f>
+        <f aca="false">TEXT(A151,"0")</f>
         <v>911313326167733</v>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
         <v>911313311383199</v>
       </c>
       <c r="B152" s="1" t="str">
-        <f aca="false">TEXT(A152, "0")</f>
+        <f aca="false">TEXT(A152,"0")</f>
         <v>911313311383199</v>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
         <v>911313349483277</v>
       </c>
       <c r="B153" s="1" t="str">
-        <f aca="false">TEXT(A153, "0")</f>
+        <f aca="false">TEXT(A153,"0")</f>
         <v>911313349483277</v>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>913313338367616</v>
       </c>
       <c r="B154" s="1" t="str">
-        <f aca="false">TEXT(A154, "0")</f>
+        <f aca="false">TEXT(A154,"0")</f>
         <v>913313338367616</v>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
         <v>911313311378824</v>
       </c>
       <c r="B155" s="1" t="str">
-        <f aca="false">TEXT(A155, "0")</f>
+        <f aca="false">TEXT(A155,"0")</f>
         <v>911313311378824</v>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
         <v>911313339963259</v>
       </c>
       <c r="B156" s="1" t="str">
-        <f aca="false">TEXT(A156, "0")</f>
+        <f aca="false">TEXT(A156,"0")</f>
         <v>911313339963259</v>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
         <v>911313347514212</v>
       </c>
       <c r="B157" s="1" t="str">
-        <f aca="false">TEXT(A157, "0")</f>
+        <f aca="false">TEXT(A157,"0")</f>
         <v>911313347514212</v>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
         <v>912313315556993</v>
       </c>
       <c r="B158" s="1" t="str">
-        <f aca="false">TEXT(A158, "0")</f>
+        <f aca="false">TEXT(A158,"0")</f>
         <v>912313315556993</v>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>912313321883258</v>
       </c>
       <c r="B159" s="1" t="str">
-        <f aca="false">TEXT(A159, "0")</f>
+        <f aca="false">TEXT(A159,"0")</f>
         <v>912313321883258</v>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
         <v>912313323251713</v>
       </c>
       <c r="B160" s="1" t="str">
-        <f aca="false">TEXT(A160, "0")</f>
+        <f aca="false">TEXT(A160,"0")</f>
         <v>912313323251713</v>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
         <v>912313321995833</v>
       </c>
       <c r="B161" s="1" t="str">
-        <f aca="false">TEXT(A161, "0")</f>
+        <f aca="false">TEXT(A161,"0")</f>
         <v>912313321995833</v>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
         <v>911313339912155</v>
       </c>
       <c r="B162" s="1" t="str">
-        <f aca="false">TEXT(A162, "0")</f>
+        <f aca="false">TEXT(A162,"0")</f>
         <v>911313339912155</v>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
         <v>911313322111511</v>
       </c>
       <c r="B163" s="1" t="str">
-        <f aca="false">TEXT(A163, "0")</f>
+        <f aca="false">TEXT(A163,"0")</f>
         <v>911313322111511</v>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
         <v>911313341376597</v>
       </c>
       <c r="B164" s="1" t="str">
-        <f aca="false">TEXT(A164, "0")</f>
+        <f aca="false">TEXT(A164,"0")</f>
         <v>911313341376597</v>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
         <v>911313346965613</v>
       </c>
       <c r="B165" s="1" t="str">
-        <f aca="false">TEXT(A165, "0")</f>
+        <f aca="false">TEXT(A165,"0")</f>
         <v>911313346965613</v>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>911313359632329</v>
       </c>
       <c r="B166" s="1" t="str">
-        <f aca="false">TEXT(A166, "0")</f>
+        <f aca="false">TEXT(A166,"0")</f>
         <v>911313359632329</v>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         <v>911313339919484</v>
       </c>
       <c r="B167" s="1" t="str">
-        <f aca="false">TEXT(A167, "0")</f>
+        <f aca="false">TEXT(A167,"0")</f>
         <v>911313339919484</v>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
         <v>911313339919147</v>
       </c>
       <c r="B168" s="1" t="str">
-        <f aca="false">TEXT(A168, "0")</f>
+        <f aca="false">TEXT(A168,"0")</f>
         <v>911313339919147</v>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
         <v>911313324321725</v>
       </c>
       <c r="B169" s="1" t="str">
-        <f aca="false">TEXT(A169, "0")</f>
+        <f aca="false">TEXT(A169,"0")</f>
         <v>911313324321725</v>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
         <v>911313341398347</v>
       </c>
       <c r="B170" s="1" t="str">
-        <f aca="false">TEXT(A170, "0")</f>
+        <f aca="false">TEXT(A170,"0")</f>
         <v>911313341398347</v>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
         <v>911313342376989</v>
       </c>
       <c r="B171" s="1" t="str">
-        <f aca="false">TEXT(A171, "0")</f>
+        <f aca="false">TEXT(A171,"0")</f>
         <v>911313342376989</v>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
         <v>911313347514225</v>
       </c>
       <c r="B172" s="1" t="str">
-        <f aca="false">TEXT(A172, "0")</f>
+        <f aca="false">TEXT(A172,"0")</f>
         <v>911313347514225</v>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
         <v>912313332837995</v>
       </c>
       <c r="B173" s="1" t="str">
-        <f aca="false">TEXT(A173, "0")</f>
+        <f aca="false">TEXT(A173,"0")</f>
         <v>912313332837995</v>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
         <v>912313332834657</v>
       </c>
       <c r="B174" s="1" t="str">
-        <f aca="false">TEXT(A174, "0")</f>
+        <f aca="false">TEXT(A174,"0")</f>
         <v>912313332834657</v>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
         <v>912313357384737</v>
       </c>
       <c r="B175" s="1" t="str">
-        <f aca="false">TEXT(A175, "0")</f>
+        <f aca="false">TEXT(A175,"0")</f>
         <v>912313357384737</v>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
         <v>912313332835788</v>
       </c>
       <c r="B176" s="1" t="str">
-        <f aca="false">TEXT(A176, "0")</f>
+        <f aca="false">TEXT(A176,"0")</f>
         <v>912313332835788</v>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
         <v>912313332835835</v>
       </c>
       <c r="B177" s="1" t="str">
-        <f aca="false">TEXT(A177, "0")</f>
+        <f aca="false">TEXT(A177,"0")</f>
         <v>912313332835835</v>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         <v>912313332835795</v>
       </c>
       <c r="B178" s="1" t="str">
-        <f aca="false">TEXT(A178, "0")</f>
+        <f aca="false">TEXT(A178,"0")</f>
         <v>912313332835795</v>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
         <v>912313357384766</v>
       </c>
       <c r="B179" s="1" t="str">
-        <f aca="false">TEXT(A179, "0")</f>
+        <f aca="false">TEXT(A179,"0")</f>
         <v>912313357384766</v>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
         <v>912313332838459</v>
       </c>
       <c r="B180" s="1" t="str">
-        <f aca="false">TEXT(A180, "0")</f>
+        <f aca="false">TEXT(A180,"0")</f>
         <v>912313332838459</v>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
         <v>912313332799768</v>
       </c>
       <c r="B181" s="1" t="str">
-        <f aca="false">TEXT(A181, "0")</f>
+        <f aca="false">TEXT(A181,"0")</f>
         <v>912313332799768</v>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         <v>912313332838442</v>
       </c>
       <c r="B182" s="1" t="str">
-        <f aca="false">TEXT(A182, "0")</f>
+        <f aca="false">TEXT(A182,"0")</f>
         <v>912313332838442</v>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
         <v>913313336421791</v>
       </c>
       <c r="B183" s="1" t="str">
-        <f aca="false">TEXT(A183, "0")</f>
+        <f aca="false">TEXT(A183,"0")</f>
         <v>913313336421791</v>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
         <v>912313332837847</v>
       </c>
       <c r="B184" s="1" t="str">
-        <f aca="false">TEXT(A184, "0")</f>
+        <f aca="false">TEXT(A184,"0")</f>
         <v>912313332837847</v>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
         <v>913313336421694</v>
       </c>
       <c r="B185" s="1" t="str">
-        <f aca="false">TEXT(A185, "0")</f>
+        <f aca="false">TEXT(A185,"0")</f>
         <v>913313336421694</v>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
         <v>912313332832632</v>
       </c>
       <c r="B186" s="1" t="str">
-        <f aca="false">TEXT(A186, "0")</f>
+        <f aca="false">TEXT(A186,"0")</f>
         <v>912313332832632</v>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         <v>913313336421827</v>
       </c>
       <c r="B187" s="1" t="str">
-        <f aca="false">TEXT(A187, "0")</f>
+        <f aca="false">TEXT(A187,"0")</f>
         <v>913313336421827</v>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
         <v>913313322796643</v>
       </c>
       <c r="B188" s="1" t="str">
-        <f aca="false">TEXT(A188, "0")</f>
+        <f aca="false">TEXT(A188,"0")</f>
         <v>913313322796643</v>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
         <v>913313323527315</v>
       </c>
       <c r="B189" s="1" t="str">
-        <f aca="false">TEXT(A189, "0")</f>
+        <f aca="false">TEXT(A189,"0")</f>
         <v>913313323527315</v>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
         <v>913313336422436</v>
       </c>
       <c r="B190" s="1" t="str">
-        <f aca="false">TEXT(A190, "0")</f>
+        <f aca="false">TEXT(A190,"0")</f>
         <v>913313336422436</v>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
         <v>913313322771793</v>
       </c>
       <c r="B191" s="1" t="str">
-        <f aca="false">TEXT(A191, "0")</f>
+        <f aca="false">TEXT(A191,"0")</f>
         <v>913313322771793</v>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
         <v>913313322771933</v>
       </c>
       <c r="B192" s="1" t="str">
-        <f aca="false">TEXT(A192, "0")</f>
+        <f aca="false">TEXT(A192,"0")</f>
         <v>913313322771933</v>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         <v>913313322771858</v>
       </c>
       <c r="B193" s="1" t="str">
-        <f aca="false">TEXT(A193, "0")</f>
+        <f aca="false">TEXT(A193,"0")</f>
         <v>913313322771858</v>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
         <v>913313323531262</v>
       </c>
       <c r="B194" s="1" t="str">
-        <f aca="false">TEXT(A194, "0")</f>
+        <f aca="false">TEXT(A194,"0")</f>
         <v>913313323531262</v>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         <v>913313321974347</v>
       </c>
       <c r="B195" s="1" t="str">
-        <f aca="false">TEXT(A195, "0")</f>
+        <f aca="false">TEXT(A195,"0")</f>
         <v>913313321974347</v>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>913313321968574</v>
       </c>
       <c r="B196" s="1" t="str">
-        <f aca="false">TEXT(A196, "0")</f>
+        <f aca="false">TEXT(A196,"0")</f>
         <v>913313321968574</v>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>8313131474929</v>
       </c>
       <c r="B197" s="1" t="str">
-        <f aca="false">TEXT(A197, "0")</f>
+        <f aca="false">TEXT(A197,"0")</f>
         <v>8313131474929</v>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>913313321975153</v>
       </c>
       <c r="B198" s="1" t="str">
-        <f aca="false">TEXT(A198, "0")</f>
+        <f aca="false">TEXT(A198,"0")</f>
         <v>913313321975153</v>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>913313321975134</v>
       </c>
       <c r="B199" s="1" t="str">
-        <f aca="false">TEXT(A199, "0")</f>
+        <f aca="false">TEXT(A199,"0")</f>
         <v>913313321975134</v>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>913313321978341</v>
       </c>
       <c r="B200" s="1" t="str">
-        <f aca="false">TEXT(A200, "0")</f>
+        <f aca="false">TEXT(A200,"0")</f>
         <v>913313321978341</v>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         <v>913313321978396</v>
       </c>
       <c r="B201" s="1" t="str">
-        <f aca="false">TEXT(A201, "0")</f>
+        <f aca="false">TEXT(A201,"0")</f>
         <v>913313321978396</v>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
         <v>913313321978334</v>
       </c>
       <c r="B202" s="1" t="str">
-        <f aca="false">TEXT(A202, "0")</f>
+        <f aca="false">TEXT(A202,"0")</f>
         <v>913313321978334</v>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
         <v>913313321981393</v>
       </c>
       <c r="B203" s="1" t="str">
-        <f aca="false">TEXT(A203, "0")</f>
+        <f aca="false">TEXT(A203,"0")</f>
         <v>913313321981393</v>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
         <v>913313321976739</v>
       </c>
       <c r="B204" s="1" t="str">
-        <f aca="false">TEXT(A204, "0")</f>
+        <f aca="false">TEXT(A204,"0")</f>
         <v>913313321976739</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
         <v>913313321968234</v>
       </c>
       <c r="B205" s="1" t="str">
-        <f aca="false">TEXT(A205, "0")</f>
+        <f aca="false">TEXT(A205,"0")</f>
         <v>913313321968234</v>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
         <v>913313321965333</v>
       </c>
       <c r="B206" s="1" t="str">
-        <f aca="false">TEXT(A206, "0")</f>
+        <f aca="false">TEXT(A206,"0")</f>
         <v>913313321965333</v>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         <v>913313321982319</v>
       </c>
       <c r="B207" s="1" t="str">
-        <f aca="false">TEXT(A207, "0")</f>
+        <f aca="false">TEXT(A207,"0")</f>
         <v>913313321982319</v>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
         <v>913313321968223</v>
       </c>
       <c r="B208" s="1" t="str">
-        <f aca="false">TEXT(A208, "0")</f>
+        <f aca="false">TEXT(A208,"0")</f>
         <v>913313321968223</v>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
         <v>913313321968217</v>
       </c>
       <c r="B209" s="1" t="str">
-        <f aca="false">TEXT(A209, "0")</f>
+        <f aca="false">TEXT(A209,"0")</f>
         <v>913313321968217</v>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
         <v>913313321977567</v>
       </c>
       <c r="B210" s="1" t="str">
-        <f aca="false">TEXT(A210, "0")</f>
+        <f aca="false">TEXT(A210,"0")</f>
         <v>913313321977567</v>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
         <v>913313321977573</v>
       </c>
       <c r="B211" s="1" t="str">
-        <f aca="false">TEXT(A211, "0")</f>
+        <f aca="false">TEXT(A211,"0")</f>
         <v>913313321977573</v>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
         <v>913313321991945</v>
       </c>
       <c r="B212" s="1" t="str">
-        <f aca="false">TEXT(A212, "0")</f>
+        <f aca="false">TEXT(A212,"0")</f>
         <v>913313321991945</v>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
         <v>913313321972766</v>
       </c>
       <c r="B213" s="1" t="str">
-        <f aca="false">TEXT(A213, "0")</f>
+        <f aca="false">TEXT(A213,"0")</f>
         <v>913313321972766</v>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
         <v>913313321962769</v>
       </c>
       <c r="B214" s="1" t="str">
-        <f aca="false">TEXT(A214, "0")</f>
+        <f aca="false">TEXT(A214,"0")</f>
         <v>913313321962769</v>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
         <v>913313321972821</v>
       </c>
       <c r="B215" s="1" t="str">
-        <f aca="false">TEXT(A215, "0")</f>
+        <f aca="false">TEXT(A215,"0")</f>
         <v>913313321972821</v>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
         <v>913313321972782</v>
       </c>
       <c r="B216" s="1" t="str">
-        <f aca="false">TEXT(A216, "0")</f>
+        <f aca="false">TEXT(A216,"0")</f>
         <v>913313321972782</v>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
         <v>913313346739638</v>
       </c>
       <c r="B217" s="1" t="str">
-        <f aca="false">TEXT(A217, "0")</f>
+        <f aca="false">TEXT(A217,"0")</f>
         <v>913313346739638</v>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
         <v>913313321973484</v>
       </c>
       <c r="B218" s="1" t="str">
-        <f aca="false">TEXT(A218, "0")</f>
+        <f aca="false">TEXT(A218,"0")</f>
         <v>913313321973484</v>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
         <v>913313321973772</v>
       </c>
       <c r="B219" s="1" t="str">
-        <f aca="false">TEXT(A219, "0")</f>
+        <f aca="false">TEXT(A219,"0")</f>
         <v>913313321973772</v>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
         <v>913313321973785</v>
       </c>
       <c r="B220" s="1" t="str">
-        <f aca="false">TEXT(A220, "0")</f>
+        <f aca="false">TEXT(A220,"0")</f>
         <v>913313321973785</v>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
         <v>913313321973798</v>
       </c>
       <c r="B221" s="1" t="str">
-        <f aca="false">TEXT(A221, "0")</f>
+        <f aca="false">TEXT(A221,"0")</f>
         <v>913313321973798</v>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
         <v>913313321973471</v>
       </c>
       <c r="B222" s="1" t="str">
-        <f aca="false">TEXT(A222, "0")</f>
+        <f aca="false">TEXT(A222,"0")</f>
         <v>913313321973471</v>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
         <v>913313321986823</v>
       </c>
       <c r="B223" s="1" t="str">
-        <f aca="false">TEXT(A223, "0")</f>
+        <f aca="false">TEXT(A223,"0")</f>
         <v>913313321986823</v>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>913313321962882</v>
       </c>
       <c r="B224" s="1" t="str">
-        <f aca="false">TEXT(A224, "0")</f>
+        <f aca="false">TEXT(A224,"0")</f>
         <v>913313321962882</v>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
         <v>913313321986846</v>
       </c>
       <c r="B225" s="1" t="str">
-        <f aca="false">TEXT(A225, "0")</f>
+        <f aca="false">TEXT(A225,"0")</f>
         <v>913313321986846</v>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
         <v>913313321966897</v>
       </c>
       <c r="B226" s="1" t="str">
-        <f aca="false">TEXT(A226, "0")</f>
+        <f aca="false">TEXT(A226,"0")</f>
         <v>913313321966897</v>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         <v>913313321958571</v>
       </c>
       <c r="B227" s="1" t="str">
-        <f aca="false">TEXT(A227, "0")</f>
+        <f aca="false">TEXT(A227,"0")</f>
         <v>913313321958571</v>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
         <v>913313321962471</v>
       </c>
       <c r="B228" s="1" t="str">
-        <f aca="false">TEXT(A228, "0")</f>
+        <f aca="false">TEXT(A228,"0")</f>
         <v>913313321962471</v>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
         <v>913313321971734</v>
       </c>
       <c r="B229" s="1" t="str">
-        <f aca="false">TEXT(A229, "0")</f>
+        <f aca="false">TEXT(A229,"0")</f>
         <v>913313321971734</v>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
         <v>913313321971624</v>
       </c>
       <c r="B230" s="1" t="str">
-        <f aca="false">TEXT(A230, "0")</f>
+        <f aca="false">TEXT(A230,"0")</f>
         <v>913313321971624</v>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
         <v>913313321971533</v>
       </c>
       <c r="B231" s="1" t="str">
-        <f aca="false">TEXT(A231, "0")</f>
+        <f aca="false">TEXT(A231,"0")</f>
         <v>913313321971533</v>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
         <v>913313321971643</v>
       </c>
       <c r="B232" s="1" t="str">
-        <f aca="false">TEXT(A232, "0")</f>
+        <f aca="false">TEXT(A232,"0")</f>
         <v>913313321971643</v>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
         <v>913313321957897</v>
       </c>
       <c r="B233" s="1" t="str">
-        <f aca="false">TEXT(A233, "0")</f>
+        <f aca="false">TEXT(A233,"0")</f>
         <v>913313321957897</v>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
         <v>914313333396328</v>
       </c>
       <c r="B234" s="1" t="str">
-        <f aca="false">TEXT(A234, "0")</f>
+        <f aca="false">TEXT(A234,"0")</f>
         <v>914313333396328</v>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
         <v>914313333395287</v>
       </c>
       <c r="B235" s="1" t="str">
-        <f aca="false">TEXT(A235, "0")</f>
+        <f aca="false">TEXT(A235,"0")</f>
         <v>914313333395287</v>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         <v>913313321963187</v>
       </c>
       <c r="B236" s="1" t="str">
-        <f aca="false">TEXT(A236, "0")</f>
+        <f aca="false">TEXT(A236,"0")</f>
         <v>913313321963187</v>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         <v>913313321958272</v>
       </c>
       <c r="B237" s="1" t="str">
-        <f aca="false">TEXT(A237, "0")</f>
+        <f aca="false">TEXT(A237,"0")</f>
         <v>913313321958272</v>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
         <v>914313333395293</v>
       </c>
       <c r="B238" s="1" t="str">
-        <f aca="false">TEXT(A238, "0")</f>
+        <f aca="false">TEXT(A238,"0")</f>
         <v>914313333395293</v>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         <v>914313333397173</v>
       </c>
       <c r="B239" s="1" t="str">
-        <f aca="false">TEXT(A239, "0")</f>
+        <f aca="false">TEXT(A239,"0")</f>
         <v>914313333397173</v>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
         <v>914313333399438</v>
       </c>
       <c r="B240" s="1" t="str">
-        <f aca="false">TEXT(A240, "0")</f>
+        <f aca="false">TEXT(A240,"0")</f>
         <v>914313333399438</v>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
         <v>914313333399467</v>
       </c>
       <c r="B241" s="1" t="str">
-        <f aca="false">TEXT(A241, "0")</f>
+        <f aca="false">TEXT(A241,"0")</f>
         <v>914313333399467</v>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
         <v>914313333399425</v>
       </c>
       <c r="B242" s="1" t="str">
-        <f aca="false">TEXT(A242, "0")</f>
+        <f aca="false">TEXT(A242,"0")</f>
         <v>914313333399425</v>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
         <v>914313333399441</v>
       </c>
       <c r="B243" s="1" t="str">
-        <f aca="false">TEXT(A243, "0")</f>
+        <f aca="false">TEXT(A243,"0")</f>
         <v>914313333399441</v>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
         <v>914313333399454</v>
       </c>
       <c r="B244" s="1" t="str">
-        <f aca="false">TEXT(A244, "0")</f>
+        <f aca="false">TEXT(A244,"0")</f>
         <v>914313333399454</v>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
         <v>914313333399496</v>
       </c>
       <c r="B245" s="1" t="str">
-        <f aca="false">TEXT(A245, "0")</f>
+        <f aca="false">TEXT(A245,"0")</f>
         <v>914313333399496</v>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
         <v>914313333433295</v>
       </c>
       <c r="B246" s="1" t="str">
-        <f aca="false">TEXT(A246, "0")</f>
+        <f aca="false">TEXT(A246,"0")</f>
         <v>914313333433295</v>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
         <v>914313333433554</v>
       </c>
       <c r="B247" s="1" t="str">
-        <f aca="false">TEXT(A247, "0")</f>
+        <f aca="false">TEXT(A247,"0")</f>
         <v>914313333433554</v>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>914313333396552</v>
       </c>
       <c r="B248" s="1" t="str">
-        <f aca="false">TEXT(A248, "0")</f>
+        <f aca="false">TEXT(A248,"0")</f>
         <v>914313333396552</v>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
         <v>914313333399412</v>
       </c>
       <c r="B249" s="1" t="str">
-        <f aca="false">TEXT(A249, "0")</f>
+        <f aca="false">TEXT(A249,"0")</f>
         <v>914313333399412</v>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
         <v>914313333433583</v>
       </c>
       <c r="B250" s="1" t="str">
-        <f aca="false">TEXT(A250, "0")</f>
+        <f aca="false">TEXT(A250,"0")</f>
         <v>914313333433583</v>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
         <v>914313333397911</v>
       </c>
       <c r="B251" s="1" t="str">
-        <f aca="false">TEXT(A251, "0")</f>
+        <f aca="false">TEXT(A251,"0")</f>
         <v>914313333397911</v>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
         <v>914313333397938</v>
       </c>
       <c r="B252" s="1" t="str">
-        <f aca="false">TEXT(A252, "0")</f>
+        <f aca="false">TEXT(A252,"0")</f>
         <v>914313333397938</v>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
         <v>914313333397898</v>
       </c>
       <c r="B253" s="1" t="str">
-        <f aca="false">TEXT(A253, "0")</f>
+        <f aca="false">TEXT(A253,"0")</f>
         <v>914313333397898</v>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
         <v>914313317339232</v>
       </c>
       <c r="B254" s="1" t="str">
-        <f aca="false">TEXT(A254, "0")</f>
+        <f aca="false">TEXT(A254,"0")</f>
         <v>914313317339232</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         <v>914313317338735</v>
       </c>
       <c r="B255" s="1" t="str">
-        <f aca="false">TEXT(A255, "0")</f>
+        <f aca="false">TEXT(A255,"0")</f>
         <v>914313317338735</v>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
         <v>914313317339258</v>
       </c>
       <c r="B256" s="1" t="str">
-        <f aca="false">TEXT(A256, "0")</f>
+        <f aca="false">TEXT(A256,"0")</f>
         <v>914313317339258</v>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
         <v>911313346969822</v>
       </c>
       <c r="B257" s="1" t="str">
-        <f aca="false">TEXT(A257, "0")</f>
+        <f aca="false">TEXT(A257,"0")</f>
         <v>911313346969822</v>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
         <v>914313317311357</v>
       </c>
       <c r="B258" s="1" t="str">
-        <f aca="false">TEXT(A258, "0")</f>
+        <f aca="false">TEXT(A258,"0")</f>
         <v>914313317311357</v>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
         <v>914313317311363</v>
       </c>
       <c r="B259" s="1" t="str">
-        <f aca="false">TEXT(A259, "0")</f>
+        <f aca="false">TEXT(A259,"0")</f>
         <v>914313317311363</v>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>914313317339847</v>
       </c>
       <c r="B260" s="1" t="str">
-        <f aca="false">TEXT(A260, "0")</f>
+        <f aca="false">TEXT(A260,"0")</f>
         <v>914313317339847</v>
       </c>
     </row>
@@ -2708,44 +2708,80 @@
       <c r="A261" s="2" t="n">
         <v>914313317311344</v>
       </c>
+      <c r="B261" s="1" t="str">
+        <f aca="false">TEXT(A261,"0")</f>
+        <v>914313317311344</v>
+      </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="2" t="n">
         <v>914313317311373</v>
       </c>
+      <c r="B262" s="1" t="str">
+        <f aca="false">TEXT(A262,"0")</f>
+        <v>914313317311373</v>
+      </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="n">
         <v>914313317313436</v>
       </c>
+      <c r="B263" s="1" t="str">
+        <f aca="false">TEXT(A263,"0")</f>
+        <v>914313317313436</v>
+      </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2" t="n">
         <v>914313317339853</v>
       </c>
+      <c r="B264" s="1" t="str">
+        <f aca="false">TEXT(A264,"0")</f>
+        <v>914313317339853</v>
+      </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2" t="n">
         <v>914313317339876</v>
       </c>
+      <c r="B265" s="1" t="str">
+        <f aca="false">TEXT(A265,"0")</f>
+        <v>914313317339876</v>
+      </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2" t="n">
         <v>914313317313782</v>
       </c>
+      <c r="B266" s="1" t="str">
+        <f aca="false">TEXT(A266,"0")</f>
+        <v>914313317313782</v>
+      </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="n">
         <v>914313317339779</v>
       </c>
+      <c r="B267" s="1" t="str">
+        <f aca="false">TEXT(A267,"0")</f>
+        <v>914313317339779</v>
+      </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2" t="n">
         <v>911313346968845</v>
       </c>
+      <c r="B268" s="1" t="str">
+        <f aca="false">TEXT(A268,"0")</f>
+        <v>911313346968845</v>
+      </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2" t="n">
+        <v>914313317338378</v>
+      </c>
+      <c r="B269" s="1" t="str">
+        <f aca="false">TEXT(A269,"0")</f>
         <v>914313317338378</v>
       </c>
     </row>
